--- a/reports/livrables/L3_diagnostic_nettoyage/diagnostic_autres_tables.xlsx
+++ b/reports/livrables/L3_diagnostic_nettoyage/diagnostic_autres_tables.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registre" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_par_annee" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_densite_releves" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_vs_ventes_mois" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_vs_ventes_annee" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offre_par_magasin" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objectifs_coefficients" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En_ligne_detail_vs_ventes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En_ligne_par_produit" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En_ligne_clients" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Registre" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stock_par_annee" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stock_densite_releves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stock_vs_ventes_mois" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stock_vs_ventes_annee" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Offre_par_magasin" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Objectifs_coefficients" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="En_ligne_detail_vs_ventes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="En_ligne_par_produit" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="En_ligne_clients" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9918448997509978</v>
+        <v>0.9918448997509977</v>
       </c>
       <c r="E3" t="n">
         <v>0.9992753004058629</v>
@@ -3206,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.988418215847103</v>
+        <v>0.9884182158471032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966653121459885</v>
+        <v>0.9966653121459886</v>
       </c>
       <c r="F4" t="n">
         <v>0.952076677316294</v>
